--- a/data/reports/report-2026-08-16.xlsx
+++ b/data/reports/report-2026-08-16.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>−25%（週+3,803円）</t>
+          <t>−25%（週+2,852円）</t>
         </is>
       </c>
     </row>
@@ -30164,7 +30164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30211,7 +30211,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>🔴 必須</t>
+          <t>✅ 判定済</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -30221,7 +30221,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>宣言済みトリガー該当。3窓(8/13-15/8/11-15/8/09-15)すべて余裕&lt;0.30（−0.41/−0.12/+0.11）、3日MER 1.18&lt;分岐1.59。限界MER×0.6/0.7/0.8の3端すべてで削減が正（+0.145〜+0.358）。7,800→5,850（−25%）</t>
+          <t>宣言済みトリガーどおり 7,800→5,850（−25%）を実施。Meta直読で daily_budget=5850 を確認。3窓すべて余裕&lt;0.30（−0.41/−0.12/+0.11）・頑健性3端一致</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -30231,24 +30231,24 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>本日</t>
+          <t>完了</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>✅ 判定済</t>
+          <t>📌 本日は広告の操作なし</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>W固定スマホ車載ホルダー</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>週次ランプ判定。W-1(8/02-08) MER 3.86 → W0(8/09-15) 2.76、Δ広告費+129,346円に対しΔ売上+246,362円で増分MER 1.90。分岐1.42超・目標2.88未満 → 40,000円で据え置き</t>
+          <t>判定日の商品はすべて処理済み。次の判定日は8/18（日傘統合・形状記憶−25%・パーカー戻し後の回復）</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -30258,7 +30258,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -30270,12 +30270,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>害虫ブロッカーの広告停止</t>
+          <t>W固定スマホ車載ホルダー</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>8/16の消化ゼロ・予算スナップショットから消滅で停止を確認。8/15は24,671円消化（DRAFT化が14:59のため日中まで稼働）。37,000円/日が解放された</t>
+          <t>週次ランプ判定。W-1(8/02-08) MER 3.86 → W0(8/09-15) 2.76、Δ広告費+129,346円に対しΔ売上+246,362円で増分MER 1.90。分岐1.42超・目標2.88未満 → 40,000円で据え置き</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -30297,12 +30297,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Supermetricsの復旧</t>
+          <t>害虫ブロッカーの広告停止</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>8/15朝から2日間取得不能だったが8/16に復旧。8/15の広告費を遡って追記し、横照合（Σキャンペーン=アカウント）で差0円を確認</t>
+          <t>8/16の消化ゼロ・予算スナップショットから消滅で停止を確認。8/15は24,671円消化（DRAFT化が14:59のため日中まで稼働）。37,000円/日が解放された</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -30319,17 +30319,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>🟡 推奨</t>
+          <t>✅ 判定済</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>空いた37,000円/日の使い道</t>
+          <t>Supermetricsの復旧</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>ユーザー判断で再配分しない。新商品テストの原資として保持（Phase1が日5,000円なので7品ぶん）。CJの原価回答が来たら着手</t>
+          <t>8/15朝から2日間取得不能だったが8/16に復旧。8/15の広告費を遡って追記し、横照合（Σキャンペーン=アカウント）で差0円を確認</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -30339,7 +30339,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原価待ち</t>
+          <t>完了</t>
         </is>
       </c>
     </row>
@@ -30351,22 +30351,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CJへの問い合わせ1通</t>
+          <t>空いた37,000円/日の使い道</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>新商品5品の見積 ／ 既存12品のACアダプタ同梱確認（PSE） ／ 主力6品の原価交渉。下書きは data/lp/cj-inquiry-2026-08-15.txt</t>
+          <t>ユーザー判断で再配分しない。新商品テストの原資として保持（Phase1が日5,000円なので7品ぶん）。CJの原価回答が来たら着手</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>上位3品−10%で月274,584円</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>本日</t>
+          <t>原価待ち</t>
         </is>
       </c>
     </row>
@@ -30378,17 +30378,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>偽カウントダウンタイマーの削除</t>
+          <t>CJへの問い合わせ1通</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>snippets/price.liquid。#minutes/#seconds が存在せず何も描画していない死んだコード。コレクションページで16個が同時に空回りしている。消してもCVRは下がらない</t>
+          <t>新商品5品の見積 ／ 既存12品のACアダプタ同梱確認（PSE） ／ 主力6品の原価交渉。下書きは data/lp/cj-inquiry-2026-08-15.txt</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>ページが軽くなる</t>
+          <t>上位3品−10%で月274,584円</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -30400,27 +30400,27 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>👀 様子見</t>
+          <t>🟡 推奨</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>形状記憶日傘</t>
+          <t>偽カウントダウンタイマーの削除</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>3窓すべて余裕&lt;0.30（−0.01/+0.09/+0.10）・頑健性3端一致で−25%の条件を満たすが、8/18の日傘統合判定を汚染するため同日にまとめて処理する</t>
+          <t>snippets/price.liquid。#minutes/#seconds が存在せず何も描画していない死んだコード。コレクションページで16個が同時に空回りしている。消してもCVRは下がらない</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>週+約5,000円</t>
+          <t>ページが軽くなる</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>本日</t>
         </is>
       </c>
     </row>
@@ -30432,17 +30432,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>日傘2種 統合判定</t>
+          <t>形状記憶日傘</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>広告費1円あたり利益を3窓で比較し、3窓すべてで低いほうを停止</t>
+          <t>3窓すべて余裕&lt;0.30（−0.01/+0.09/+0.10）・頑健性3端一致で−25%の条件を満たすが、8/18の日傘統合判定を汚染するため同日にまとめて処理する</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>週+約5,000円</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -30459,12 +30459,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>接触冷感UVパーカー(戻し後)</t>
+          <t>日傘2種 統合判定</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>3,980円へ戻したあとの回復確認。3日MERが分岐1.56を超えれば回復。※8/13-15は4,980円と3,980円が混在し分岐も1.404/1.563で違うため、今の3窓判定（3日MER 1.02）は比較として成立しない。8/16-18のクリーンな窓で判定する</t>
+          <t>広告費1円あたり利益を3窓で比較し、3窓すべてで低いほうを停止</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -30481,17 +30481,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>✅ 判定済</t>
+          <t>👀 様子見</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ナノバブルシャワーヘッド</t>
+          <t>接触冷感UVパーカー(戻し後)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>8/16にユーザー判断で停止（宣言済みの中間判定8/18を待たず）。2日で広告10,611円・クリック186・注文1件。宣言基準のCTRは5.88%/5.95%で基準2.5%を大きく上回り素材は合格だった。落ちたのはCVR 0.92%だが注文1件では判定できない</t>
+          <t>3,980円へ戻したあとの回復確認。3日MERが分岐1.56を超えれば回復。※8/13-15は4,980円と3,980円が混在し分岐も1.404/1.563で違うため、今の3窓判定（3日MER 1.02）は比較として成立しない。8/16-18のクリーンな窓で判定する</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -30501,24 +30501,24 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>👀 様子見</t>
+          <t>✅ 判定済</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>快適マジックインソール</t>
+          <t>ナノバブルシャワーヘッド</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>本判定。7日CPA&lt;3,303円で合格 → 12,000→15,000。ただし週消化率が55.8%で増額の前提（95%）を欠くため、合格でも増額は見送る可能性が高い</t>
+          <t>8/16にユーザー判断で停止（宣言済みの中間判定8/18を待たず）。2日で広告10,611円・クリック186・注文1件。宣言基準のCTRは5.88%/5.95%で基準2.5%を大きく上回り素材は合格だった。落ちたのはCVR 0.92%だが注文1件では判定できない</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -30528,7 +30528,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>完了</t>
         </is>
       </c>
     </row>
@@ -30540,74 +30540,101 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>関連商品セクション</t>
+          <t>快適マジックインソール</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>8/14 20:21に全35商品で表示開始。W固定+2WAY合算のCVRが4.004%を割ったら即オフ、横ばい以上かつ点数/注文≥1.199で維持</t>
+          <t>本判定。7日CPA&lt;3,303円で合格 → 12,000→15,000。ただし週消化率が55.8%で増額の前提（95%）を欠くため、合格でも増額は見送る可能性が高い</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>週+1〜4万円</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>8/22</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>📌 記録</t>
+          <t>👀 様子見</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ナノバブルの再挑戦条件</t>
+          <t>関連商品セクション</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>素材(CTR 5.9%)は合格していたので次も同じ素材で良い。未検証なのは価格6,980円とLP。LP変更3箇所のうち②節水の前出しは未適用のまま。再開するなら①価格5,980円を試す ②②を適用する ③日予算7,000円で7日=49,000円まで回して注文50件に近づける、のいずれか</t>
+          <t>8/14 20:21に全35商品で表示開始。W固定+2WAY合算のCVRが4.004%を割ったら即オフ、横ばい以上かつ点数/注文≥1.199で維持</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>週+1〜4万円</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>9月以降</t>
+          <t>8/22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>📌 記録</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>ナノバブルの再挑戦条件</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>素材(CTR 5.9%)は合格していたので次も同じ素材で良い。未検証なのは価格6,980円とLP。LP変更3箇所のうち②節水の前出しは未適用のまま。再開するなら①価格5,980円を試す ②②を適用する ③日予算7,000円で7日=49,000円まで回して注文50件に近づける、のいずれか</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>9月以降</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>👀 様子見</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>安全弁（毎朝チェック）</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>全店MERが実効分岐1.42を2日連続で下回ったら赤字商品を一律−25%／単日で1.20を下回ったらその日の赤字商品を即停止。8/15は2.11</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>毎日</t>
         </is>
@@ -74732,7 +74759,7 @@
         <v>3957</v>
       </c>
       <c r="W18" s="5" t="n">
-        <v>7800</v>
+        <v>5850</v>
       </c>
       <c r="X18" s="4" t="inlineStr">
         <is>
@@ -75377,8 +75404,10 @@
       <c r="V26" s="5" t="n">
         <v>4725</v>
       </c>
-      <c r="W26" s="5" t="n">
-        <v>10000</v>
+      <c r="W26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X26" s="4" t="inlineStr">
         <is>
@@ -75843,7 +75872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -76250,79 +76279,79 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>5WAY腰掛けファン</t>
+          <t>姿勢サポートチェア</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>季節</t>
+          <t>通年</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>7800</v>
+        <v>10000</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.908</v>
+        <v>0.998</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.7</v>
+        <v>2.53</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>-0.279</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>3803</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>-3803</v>
+        <v>1.06</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>-3645</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>3645</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>2696</v>
+        <v>50718</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>姿勢サポートチェア</t>
+          <t>5WAY腰掛けファン</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>通年</t>
+          <t>季節</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>10000</v>
+        <v>5850</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.998</v>
+        <v>0.908</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.53</v>
+        <v>1.7</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>-3645</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>3645</v>
+        <v>0.05</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>-0.279</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2852</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>-2852</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>50718</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="16">
@@ -76445,7 +76474,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>ナノバブルシャワーヘッド</t>
+          <t>バランスケアスリッパ</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -76454,35 +76483,37 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D19" s="6" t="inlineStr"/>
+        <v>5000</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E19" s="4" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>-1214</v>
+        <v>-554</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1214</v>
+        <v>554</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>3264</v>
+        <v>18159</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>バランスケアスリッパ</t>
+          <t>2WAYシートボックス</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -76491,69 +76522,30 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>0.905</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.063</v>
+        <v>0.008</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>-554</v>
+        <v>-210</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>554</v>
+        <v>210</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>18159</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>2WAYシートボックス</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>通年</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>-210</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="K21" s="5" t="n">
         <v>44221</v>
       </c>
     </row>
